--- a/docs/EVAL_REPORT.xlsx
+++ b/docs/EVAL_REPORT.xlsx
@@ -11,8 +11,10 @@
     <sheet name="계층기여(dev-context)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="관측지표(dev)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="인용분석" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="한계·주석" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="컬럼설명" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="유형별검색품질" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="라우팅감사" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="한계·주석" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="컬럼설명" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1260,6 +1262,4368 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>corpus</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>config</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>context_precision</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>context_recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.964</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.878</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.917</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.917</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.917</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.917</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.382</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>R0-sql</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>R0-vec</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.766</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>R0-both</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>E2-e2e</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>corpus</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>qid</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expected_route</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>actual_route</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>router_stage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>expected_history</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>actual_history</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>route_match</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>history_match</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>mismatch</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Modu 앱의 핵심 콘셉트는 무엇인가?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>앱 개발 프레임워크로 Flutter를 선택한 이유는?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>백엔드에 PostgreSQL(PostGIS)을 선택한 이유는?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>이메일 발송 서비스로 AWS SES를 선택한 이유는?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>관심사 카테고리는 어떻게 구성되었는가?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>애플 로그인을 추가하게 된 이유는?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>모임 생성 시 인원 제한은 어떻게 정해졌는가?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>클로즈드 베타 테스트를 강남·판교 지역으로 한정한 이유는?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>마케팅 푸시 알림을 MVP에서 제외한 이유는?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>모임 탐색 화면은 어떤 방식으로 구현하기로 했는가?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>로그인 방식에 대한 결정은 프로젝트 진행 중 어떻게 바뀌었는가?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>출시 목표일은 처음 언제였고, 최종적으로 언제로 바뀌었는가?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>출시일이 연기된 근본 원인을 거슬러 올라가면 어떤 결정 때문인가?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>실시간 채팅 기능은 결정이 번복되었는가?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>history_rule</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>이메일 인증 방식의 어떤 문제가 로그인 방식 변경을 촉발했는가?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>출시일 조정 시 검토한 3가지 시나리오는 무엇이었고 왜 B안이 선택되었는가?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>소셜 로그인은 MVP 포함에서 제외되었다가 다시 포함되었는가, 아니면 처음부터 포함이었는가?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>베타 테스트 결과 중 리텐션(7일 유지율)은 몇 %였는가?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5/11 시점에 실시간 채팅을 출시에 넣지 않기로 한 결정적 이유는?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>5/18 출시일은 4/6 이후 또 바뀌었는가?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>카카오/구글/애플 소셜 로그인 SDK 연동은 누가 담당했는가?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>이메일 인증 스팸 문제 개선(SPF/DKIM 설정)은 누가 담당했는가?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>베타 테스터 100명 모집은 누가 담당했는가?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Modu 앱의 개발에 투입된 총 예산은 얼마인가?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>정식 출시 후 실제 다운로드 수나 가입자 수는 얼마였는가?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>지도 마커 미표시 버그와 소셜 로그인 프로필 누락 버그는 각각 누가 수정했는가?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Modu 앱의 경쟁 앱 3종의 구체적인 이름은 무엇인가?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>모임 알림 지연 문제는 누가, 어떻게 해결했는가?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1.1 업데이트 이후 2.0 버전에는 어떤 기능이 들어가는가?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>modu</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>실시간 채팅 WebSocket 개발 착수는 누가 담당하며 언제 시작하는가?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>파인튜닝을 이번 유지보수에서 제외하기로 한 이유는?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H32" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" t="b">
+        <v>1</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>챗봇의 반품 관련 질문 오답률이 높았던 핵심 원인은?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H33" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>chunk 분할 방식을 고정 길이에서 의미 단위(semantic)로 바꾼 이유는?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>history_rule</t>
+        </is>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>re-ranking을 정식 도입하기로 결정한 근거 수치는?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1차 개선 배포일은 언제로, 왜 그 날짜로 정했는가?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
+      </c>
+      <c r="K36" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>멀티턴 맥락 유지 기능을 1차가 아닌 2차 배포로 분리한 이유는?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LLM 모델을 최신 버전으로 업데이트하기로 한 이유와 예상 비용 증가는?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>진단 스프린트를 먼저 진행하기로 한 이유는?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>회원/포인트 영역의 정답률이 다른 영역보다 낮았던 이유는?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
+      </c>
+      <c r="K40" t="b">
+        <v>1</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>배포 후 모니터링 계획은 구체적으로 무엇인가?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>최종(6/27 기준) 전체 정답률은 몇 %이며, 개선 전 대비 몇 %p 향상됐는가?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H42" t="b">
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>영역별 정답률 변화 중 re-ranking 도입 효과가 가장 명확하게 나타난 영역은?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H43" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+      <c r="K43" t="b">
+        <v>1</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[충돌 탐지] 파인튜닝에 대한 팀의 입장은 6/16과 6/27에 동일한가?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="b">
+        <v>1</v>
+      </c>
+      <c r="L44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[충돌 탐지] re-ranking 도입 여부는 회의마다 어떻게 바뀌었는가?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>반품 영역의 정답률은 개선 전부터 최종까지 어떻게 변화했는가?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H46" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>응답 시간은 1차 개선 후와 re-ranking 도입 후 각각 어떻게 변했는가?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="b">
+        <v>1</v>
+      </c>
+      <c r="L47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>conflict_negative</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[충돌 탐지] 멀티턴 맥락 유지 기능의 우선순위나 처리 방향이 회의마다 달라졌는가?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>테스트 중 발견된 할루시네이션 사례는 몇 건이며 원인은?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>자체 QA 테스트(6/9)에서 측정한 오답률은 몇 %였는가?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>B10</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>decision</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>하루 평균 질의 건수와 fallback 응답 비율(개선 전)은 얼마였는가?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H51" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+      <c r="K51" t="b">
+        <v>1</v>
+      </c>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>지식 베이스 전면 갱신과 semantic chunking 구현은 각각 누가 담당했는가?</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H52" t="b">
+        <v>0</v>
+      </c>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+      <c r="K52" t="b">
+        <v>1</v>
+      </c>
+      <c r="L52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2차 개선 항목 중 우선순위가 '높음'으로 분류된 항목은 무엇인가?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H53" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+      <c r="K53" t="b">
+        <v>1</v>
+      </c>
+      <c r="L53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1차 개선 프로덕션 배포는 누가, 언제 담당했는가?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H54" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+      <c r="K54" t="b">
+        <v>1</v>
+      </c>
+      <c r="L54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[문서에 없음] 이 프로젝트에서 사용한 벡터 데이터베이스의 제품명(예: ChromaDB, Pinecone 등)은 무엇인가?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[문서에 없음] 그린커머스의 계약 연장 여부는 최종적으로 어떻게 결정되었는가?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H56" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>멀티턴 기능 설계 문서 작성은 누가 담당하며 마감은 언제인가?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H57" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+      <c r="K57" t="b">
+        <v>1</v>
+      </c>
+      <c r="L57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>[문서에 없음] 그린커머스 CS-Bot에 사용된 임베딩 모델의 정확한 이름과 차원 수는?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>llm</t>
+        </is>
+      </c>
+      <c r="H58" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
+      </c>
+      <c r="K58" t="b">
+        <v>1</v>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>회원/포인트 관련 공개 문서를 지식 베이스에 추가하는 작업은 누가, 언제까지 담당했는가?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+      <c r="K59" t="b">
+        <v>1</v>
+      </c>
+      <c r="L59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>hallucination</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[문서에 없음] 이번 유지보수 전체에 투입된 총 인건비 또는 프로젝트 비용은 얼마인가?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>overview</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H60" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+      <c r="K60" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>csbot</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>배포 후 3일 시점 QA 재측정은 누가 담당하며 언제 실시되는가?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>semantic</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>filter_lookup</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1344,7 +5708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/EVAL_REPORT.xlsx
+++ b/docs/EVAL_REPORT.xlsx
@@ -5624,10 +5624,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -5682,24 +5682,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>routing/chain</t>
+          <t>라우팅 감사</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>관측 지표(합격 조건 아님). 다수 문항 LLM 폴백이라 비결정 가능.</t>
+          <t>route(semantic/filter_lookup/overview)는 LLM 폴백이라 비결정 가능. 단 history_mode는 정규식이라 결정론적.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chain_inclusion(modu E2-e2e)</t>
+          <t>이력 감지(history_mode)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0 — 이력 체인 포함이 기대만큼 안 됨. TASK-007 범위 밖 후속 진단 대상.</t>
+          <t>정규식(detect_history_intent)으로만 켜짐(LLM은 route만). conflict 표현('바뀌었는가' 등)을 못 잡아 재현율 0% — 재현성 아닌 recall 문제. 개선=TASK-008(선행), supersede correctness=TASK-009.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>chain_inclusion</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>이력 라우팅 작동 지표가 아님 — pair old/new 문구가 검색 컨텍스트에 있는지만 검사(일반 검색으로도 통과, csbot 1.0이 그 경우).</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5837,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>이력 체인 포함률(E2, 기대 pair 문구 포함) — 높을수록 좋음</t>
+          <t>pair old/new 문구가 검색 컨텍스트에 포함됐는지 검사(E2) — 이력 라우팅 작동 여부가 아님(일반 검색으로도 통과)</t>
         </is>
       </c>
     </row>
